--- a/Section 3.0/Data_section3.0.xlsx
+++ b/Section 3.0/Data_section3.0.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Comsol_Tut\EquationBasedModelling\HTO_paper_models\latest_model_tcd\Neom_report_models\Publication Models\modified_model\Optimization_study\saved data\Joule_submission_docs\Section 3.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KUNTEAM\Documents\GitHub\Physics-informed-multiscale-optimization-of-renewable-powered-alkaline-water-electrolysis\Section 3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FFF839-23AE-40D0-A6F0-982BC0ECA7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -182,13 +182,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -595,36 +595,36 @@
       <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
       <c r="H6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
       <c r="T6" s="4"/>
-      <c r="V6" s="10" t="s">
+      <c r="V6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="AA6" s="10" t="s">
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="AA6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AB6" s="10"/>
-      <c r="AC6" s="10"/>
-      <c r="AD6" s="10"/>
-      <c r="AE6" s="10"/>
+      <c r="AB6" s="8"/>
+      <c r="AC6" s="8"/>
+      <c r="AD6" s="8"/>
+      <c r="AE6" s="8"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
@@ -1223,13 +1223,13 @@
       <c r="F17">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
       <c r="V17">
         <v>50.406590000000001</v>
       </c>
@@ -9279,11 +9279,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AC7:AD7"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="V6:X6"/>
-    <mergeCell ref="AA6:AE6"/>
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="H6:S6"/>
@@ -9297,6 +9292,11 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="N7:O7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AC7:AD7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="V6:X6"/>
+    <mergeCell ref="AA6:AE6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
